--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>5.97</v>
+        <v>4.82</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.7</v>
+        <v>3.76</v>
       </c>
       <c r="R42" t="n">
-        <v>5.41</v>
+        <v>3.46</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>8.25</v>
+        <v>2.27</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.68</v>
+        <v>4.49</v>
       </c>
       <c r="R44" t="n">
-        <v>2.5</v>
+        <v>4.18</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.99</v>
+        <v>1.36</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.85</v>
+        <v>8.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R79" t="n">
-        <v>3.69</v>
+        <v>4.27</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>4.22</v>
       </c>
       <c r="R85" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.69</v>
+        <v>8</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.67</v>
+        <v>4.68</v>
       </c>
       <c r="R114" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q115" t="n">
-        <v>5.8</v>
+        <v>3.58</v>
       </c>
       <c r="R115" t="n">
-        <v>8.65</v>
+        <v>2.85</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>8</v>
+        <v>2.69</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.68</v>
+        <v>3.67</v>
       </c>
       <c r="R118" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
-        <v>2.22</v>
+        <v>4.44</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.98</v>
+        <v>3.01</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R132" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R138" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q141" t="n">
         <v>3.6</v>
       </c>
       <c r="R141" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="R143" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="Q146" t="n">
-        <v>6.35</v>
+        <v>3.44</v>
       </c>
       <c r="R146" t="n">
-        <v>9</v>
+        <v>3.49</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R150" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.44</v>
+        <v>6.35</v>
       </c>
       <c r="R151" t="n">
-        <v>3.49</v>
+        <v>9</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30347,7 +30347,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30544,7 +30544,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.84</v>
+        <v>2.73</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="R162" t="n">
-        <v>4.42</v>
+        <v>2.58</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF165" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>5.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q168" t="n">
-        <v>5.56</v>
+        <v>3.4</v>
       </c>
       <c r="R168" t="n">
-        <v>1.5</v>
+        <v>3.54</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="Q171" t="n">
-        <v>5.75</v>
+        <v>3.71</v>
       </c>
       <c r="R171" t="n">
-        <v>8.75</v>
+        <v>2.68</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q172" t="n">
         <v>3.71</v>
       </c>
       <c r="R172" t="n">
-        <v>2.68</v>
+        <v>5.15</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="R175" t="n">
-        <v>5.04</v>
+        <v>2.78</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.64</v>
+        <v>3.81</v>
       </c>
       <c r="R177" t="n">
-        <v>7.9</v>
+        <v>5.04</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF208" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI208"/>
+  <dimension ref="A1:BI212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>5.97</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.7</v>
+        <v>5.97</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.71</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>5.41</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.72</v>
+        <v>3.99</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="R44" t="n">
-        <v>4.18</v>
+        <v>1.85</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="R47" t="n">
-        <v>5.41</v>
+        <v>8.25</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.36</v>
+        <v>2.71</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.9</v>
+        <v>3.68</v>
       </c>
       <c r="R49" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="R72" t="n">
-        <v>3.6</v>
+        <v>4.22</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R85" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46159.47916666666</v>
+        <v>46159.45833333334</v>
       </c>
     </row>
     <row r="87">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18281,27 +18281,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46159.5</v>
+        <v>46159.47916666666</v>
       </c>
     </row>
     <row r="92">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.8</v>
+        <v>3.71</v>
       </c>
       <c r="R106" t="n">
-        <v>8.65</v>
+        <v>3.69</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>4.23</v>
+        <v>2.69</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="R117" t="n">
-        <v>1.97</v>
+        <v>2.69</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46159.52083333334</v>
+        <v>46159.5</v>
       </c>
     </row>
     <row r="120">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46159.52083333334</v>
+        <v>46159.5</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46159.54166666666</v>
+        <v>46159.52083333334</v>
       </c>
     </row>
     <row r="122">
@@ -24388,27 +24388,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46159.54166666666</v>
+        <v>46159.52083333334</v>
       </c>
     </row>
     <row r="123">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25964,27 +25964,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46159.55208333334</v>
+        <v>46159.54166666666</v>
       </c>
     </row>
     <row r="131">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46159.55208333334</v>
+        <v>46159.54166666666</v>
       </c>
     </row>
     <row r="132">
@@ -26358,27 +26358,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46159.5625</v>
+        <v>46159.55208333334</v>
       </c>
     </row>
     <row r="133">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46159.5625</v>
+        <v>46159.55208333334</v>
       </c>
     </row>
     <row r="134">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46159.57291666666</v>
+        <v>46159.5625</v>
       </c>
     </row>
     <row r="138">
@@ -27540,27 +27540,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46159.58333333334</v>
+        <v>46159.5625</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R139" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46159.58333333334</v>
+        <v>46159.5625</v>
       </c>
     </row>
     <row r="140">
@@ -27934,27 +27934,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46159.58333333334</v>
+        <v>46159.57291666666</v>
       </c>
     </row>
     <row r="141">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q141" t="n">
         <v>3.6</v>
       </c>
       <c r="R141" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R143" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R146" t="n">
-        <v>3.49</v>
+        <v>2.84</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.95</v>
+        <v>4.25</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R148" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R149" t="n">
-        <v>2.84</v>
+        <v>6.05</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>4.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.25</v>
+        <v>3.44</v>
       </c>
       <c r="R150" t="n">
-        <v>1.78</v>
+        <v>3.49</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.31</v>
+        <v>2.33</v>
       </c>
       <c r="Q151" t="n">
-        <v>6.35</v>
+        <v>3.24</v>
       </c>
       <c r="R151" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30347,17 +30347,17 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46159.625</v>
+        <v>46159.58333333334</v>
       </c>
     </row>
     <row r="153">
@@ -30495,27 +30495,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46159.625</v>
+        <v>46159.58333333334</v>
       </c>
     </row>
     <row r="154">
@@ -30692,27 +30692,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46159.625</v>
+        <v>46159.58333333334</v>
       </c>
     </row>
     <row r="155">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46159.63541666666</v>
+        <v>46159.625</v>
       </c>
     </row>
     <row r="157">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46159.63541666666</v>
+        <v>46159.625</v>
       </c>
     </row>
     <row r="158">
@@ -31480,12 +31480,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46159.63541666666</v>
+        <v>46159.625</v>
       </c>
     </row>
     <row r="159">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46159.64583333334</v>
+        <v>46159.625</v>
       </c>
     </row>
     <row r="160">
@@ -31874,27 +31874,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32062,7 +32062,7 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>46159.64583333334</v>
+        <v>46159.63541666666</v>
       </c>
     </row>
     <row r="161">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46159.64583333334</v>
+        <v>46159.63541666666</v>
       </c>
     </row>
     <row r="162">
@@ -32268,27 +32268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46159.66666666666</v>
+        <v>46159.63541666666</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46159.66666666666</v>
+        <v>46159.64583333334</v>
       </c>
     </row>
     <row r="164">
@@ -32662,12 +32662,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46159.66666666666</v>
+        <v>46159.64583333334</v>
       </c>
     </row>
     <row r="165">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33047,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>46159.66666666666</v>
+        <v>46159.64583333334</v>
       </c>
     </row>
     <row r="166">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q171" t="n">
         <v>3.71</v>
       </c>
       <c r="R171" t="n">
-        <v>2.68</v>
+        <v>5.15</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.81</v>
+        <v>5.87</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.71</v>
+        <v>5.56</v>
       </c>
       <c r="R172" t="n">
-        <v>5.15</v>
+        <v>1.5</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.78</v>
+        <v>2.07</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.39</v>
+        <v>3.93</v>
       </c>
       <c r="R175" t="n">
-        <v>2.78</v>
+        <v>3.62</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35814,27 +35814,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36002,7 +36002,7 @@
         <v>0</v>
       </c>
       <c r="BI180" s="3" t="n">
-        <v>46159.67708333334</v>
+        <v>46159.66666666666</v>
       </c>
     </row>
     <row r="181">
@@ -36011,27 +36011,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36199,7 +36199,7 @@
         <v>0</v>
       </c>
       <c r="BI181" s="3" t="n">
-        <v>46159.6875</v>
+        <v>46159.66666666666</v>
       </c>
     </row>
     <row r="182">
@@ -36208,27 +36208,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36396,7 +36396,7 @@
         <v>0</v>
       </c>
       <c r="BI182" s="3" t="n">
-        <v>46159.70833333334</v>
+        <v>46159.66666666666</v>
       </c>
     </row>
     <row r="183">
@@ -36405,27 +36405,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36593,7 +36593,7 @@
         <v>0</v>
       </c>
       <c r="BI183" s="3" t="n">
-        <v>46159.70833333334</v>
+        <v>46159.66666666666</v>
       </c>
     </row>
     <row r="184">
@@ -36602,27 +36602,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36790,7 +36790,7 @@
         <v>0</v>
       </c>
       <c r="BI184" s="3" t="n">
-        <v>46159.72916666666</v>
+        <v>46159.67708333334</v>
       </c>
     </row>
     <row r="185">
@@ -36799,12 +36799,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36987,7 +36987,7 @@
         <v>0</v>
       </c>
       <c r="BI185" s="3" t="n">
-        <v>46159.75</v>
+        <v>46159.6875</v>
       </c>
     </row>
     <row r="186">
@@ -36996,12 +36996,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37184,7 +37184,7 @@
         <v>0</v>
       </c>
       <c r="BI186" s="3" t="n">
-        <v>46159.75</v>
+        <v>46159.70833333334</v>
       </c>
     </row>
     <row r="187">
@@ -37193,12 +37193,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37381,7 +37381,7 @@
         <v>0</v>
       </c>
       <c r="BI187" s="3" t="n">
-        <v>46159.76041666666</v>
+        <v>46159.70833333334</v>
       </c>
     </row>
     <row r="188">
@@ -37390,12 +37390,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37578,7 +37578,7 @@
         <v>0</v>
       </c>
       <c r="BI188" s="3" t="n">
-        <v>46159.77083333334</v>
+        <v>46159.72916666666</v>
       </c>
     </row>
     <row r="189">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="BI189" s="3" t="n">
-        <v>46159.77083333334</v>
+        <v>46159.75</v>
       </c>
     </row>
     <row r="190">
@@ -37784,12 +37784,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37972,7 +37972,7 @@
         <v>0</v>
       </c>
       <c r="BI190" s="3" t="n">
-        <v>46159.77083333334</v>
+        <v>46159.75</v>
       </c>
     </row>
     <row r="191">
@@ -37981,12 +37981,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38169,7 +38169,7 @@
         <v>0</v>
       </c>
       <c r="BI191" s="3" t="n">
-        <v>46159.77083333334</v>
+        <v>46159.76041666666</v>
       </c>
     </row>
     <row r="192">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38572,12 +38572,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38760,7 +38760,7 @@
         <v>0</v>
       </c>
       <c r="BI194" s="3" t="n">
-        <v>46159.79166666666</v>
+        <v>46159.77083333334</v>
       </c>
     </row>
     <row r="195">
@@ -38769,12 +38769,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38957,7 +38957,7 @@
         <v>0</v>
       </c>
       <c r="BI195" s="3" t="n">
-        <v>46159.79166666666</v>
+        <v>46159.77083333334</v>
       </c>
     </row>
     <row r="196">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="R196" t="n">
-        <v>2.07</v>
+        <v>3.21</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="BI196" s="3" t="n">
-        <v>46159.8125</v>
+        <v>46159.77083333334</v>
       </c>
     </row>
     <row r="197">
@@ -39163,12 +39163,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
-        <v>46159.83333333334</v>
+        <v>46159.77083333334</v>
       </c>
     </row>
     <row r="198">
@@ -39360,12 +39360,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39548,7 +39548,7 @@
         <v>0</v>
       </c>
       <c r="BI198" s="3" t="n">
-        <v>46159.83333333334</v>
+        <v>46159.79166666666</v>
       </c>
     </row>
     <row r="199">
@@ -39557,12 +39557,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39745,7 +39745,7 @@
         <v>0</v>
       </c>
       <c r="BI199" s="3" t="n">
-        <v>46159.83333333334</v>
+        <v>46159.79166666666</v>
       </c>
     </row>
     <row r="200">
@@ -39754,12 +39754,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39942,7 +39942,7 @@
         <v>0</v>
       </c>
       <c r="BI200" s="3" t="n">
-        <v>46159.84027777778</v>
+        <v>46159.8125</v>
       </c>
     </row>
     <row r="201">
@@ -39951,12 +39951,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40139,7 +40139,7 @@
         <v>0</v>
       </c>
       <c r="BI201" s="3" t="n">
-        <v>46159.85416666666</v>
+        <v>46159.83333333334</v>
       </c>
     </row>
     <row r="202">
@@ -40148,12 +40148,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40336,7 +40336,7 @@
         <v>0</v>
       </c>
       <c r="BI202" s="3" t="n">
-        <v>46159.85416666666</v>
+        <v>46159.83333333334</v>
       </c>
     </row>
     <row r="203">
@@ -40345,12 +40345,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40533,7 +40533,7 @@
         <v>0</v>
       </c>
       <c r="BI203" s="3" t="n">
-        <v>46159.875</v>
+        <v>46159.83333333334</v>
       </c>
     </row>
     <row r="204">
@@ -40542,12 +40542,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40730,7 +40730,7 @@
         <v>0</v>
       </c>
       <c r="BI204" s="3" t="n">
-        <v>46159.875</v>
+        <v>46159.84027777778</v>
       </c>
     </row>
     <row r="205">
@@ -40739,12 +40739,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40927,7 +40927,7 @@
         <v>0</v>
       </c>
       <c r="BI205" s="3" t="n">
-        <v>46159.875</v>
+        <v>46159.85416666666</v>
       </c>
     </row>
     <row r="206">
@@ -40936,12 +40936,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41124,7 +41124,7 @@
         <v>0</v>
       </c>
       <c r="BI206" s="3" t="n">
-        <v>46159.89583333334</v>
+        <v>46159.85416666666</v>
       </c>
     </row>
     <row r="207">
@@ -41133,12 +41133,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41321,7 +41321,7 @@
         <v>0</v>
       </c>
       <c r="BI207" s="3" t="n">
-        <v>46159.91666666666</v>
+        <v>46159.875</v>
       </c>
     </row>
     <row r="208">
@@ -41330,12 +41330,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41518,6 +41518,794 @@
         <v>0</v>
       </c>
       <c r="BI208" s="3" t="n">
+        <v>46159.875</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI209" s="3" t="n">
+        <v>46159.875</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0</v>
+      </c>
+      <c r="X210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI210" s="3" t="n">
+        <v>46159.89583333334</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes II</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI211" s="3" t="n">
+        <v>46159.91666666666</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI212" s="3" t="n">
         <v>46159.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>4.49</v>
       </c>
       <c r="R43" t="n">
-        <v>2.27</v>
+        <v>4.18</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.99</v>
+        <v>3.76</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>3.46</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.07</v>
+        <v>2.71</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.99</v>
+        <v>3.68</v>
       </c>
       <c r="R45" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>3.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="R48" t="n">
-        <v>4.18</v>
+        <v>1.85</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.76</v>
+        <v>4.7</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>5.41</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="R77" t="n">
-        <v>3.6</v>
+        <v>4.22</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>3.72</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R79" t="n">
-        <v>3.69</v>
+        <v>2</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R85" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="R108" t="n">
-        <v>3.33</v>
+        <v>8.65</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>4.23</v>
+        <v>8</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.71</v>
+        <v>4.68</v>
       </c>
       <c r="R109" t="n">
-        <v>1.97</v>
+        <v>1.48</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>8</v>
+        <v>2.11</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.68</v>
+        <v>3.71</v>
       </c>
       <c r="R111" t="n">
-        <v>1.48</v>
+        <v>3.69</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R129" t="n">
-        <v>3.98</v>
+        <v>2.22</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.52</v>
+        <v>3.01</v>
       </c>
       <c r="Q134" t="n">
         <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>2.91</v>
+        <v>2.47</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R141" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="Q145" t="n">
-        <v>6.35</v>
+        <v>3.44</v>
       </c>
       <c r="R145" t="n">
-        <v>9</v>
+        <v>3.49</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R146" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>4.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R148" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="R149" t="n">
-        <v>6.05</v>
+        <v>2.87</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.44</v>
+        <v>6.35</v>
       </c>
       <c r="R150" t="n">
-        <v>3.49</v>
+        <v>9</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="Q152" t="n">
         <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="R153" t="n">
-        <v>3.32</v>
+        <v>6.05</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R154" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q170" t="n">
-        <v>5.75</v>
+        <v>3.68</v>
       </c>
       <c r="R170" t="n">
-        <v>8.75</v>
+        <v>4.42</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.81</v>
+        <v>5.87</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.71</v>
+        <v>5.56</v>
       </c>
       <c r="R171" t="n">
-        <v>5.15</v>
+        <v>1.5</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.87</v>
+        <v>2.73</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.56</v>
+        <v>3.82</v>
       </c>
       <c r="R172" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="Q181" t="n">
-        <v>4.64</v>
+        <v>3.71</v>
       </c>
       <c r="R181" t="n">
-        <v>7.9</v>
+        <v>5.15</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R183" t="n">
-        <v>5.04</v>
+        <v>8.75</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="R38" t="n">
-        <v>2.27</v>
+        <v>5.41</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.9</v>
+        <v>4.49</v>
       </c>
       <c r="R42" t="n">
-        <v>8.25</v>
+        <v>4.18</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>3.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="R44" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>3.46</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.99</v>
+        <v>1.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="R48" t="n">
-        <v>1.85</v>
+        <v>8.25</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R49" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R49" t="n">
-        <v>2.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>4.22</v>
       </c>
       <c r="R76" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>4.22</v>
+        <v>3.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.72</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>2</v>
+        <v>3.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="R105" t="n">
-        <v>3.33</v>
+        <v>3.69</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.69</v>
+        <v>8</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.67</v>
+        <v>4.68</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>8</v>
+        <v>2.69</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.68</v>
+        <v>3.67</v>
       </c>
       <c r="R109" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="R110" t="n">
-        <v>1.97</v>
+        <v>3.33</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R131" t="n">
-        <v>3.98</v>
+        <v>2.22</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="R138" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH138" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.6</v>
+        <v>1.31</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.4</v>
+        <v>6.35</v>
       </c>
       <c r="R141" t="n">
-        <v>2.84</v>
+        <v>9</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R145" t="n">
-        <v>3.49</v>
+        <v>2.87</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R146" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R148" t="n">
-        <v>4.4</v>
+        <v>3.32</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="R149" t="n">
-        <v>2.87</v>
+        <v>6.05</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.31</v>
+        <v>2.33</v>
       </c>
       <c r="Q150" t="n">
-        <v>6.35</v>
+        <v>3.24</v>
       </c>
       <c r="R150" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q152" t="n">
         <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R153" t="n">
-        <v>6.05</v>
+        <v>2.84</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>4.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R154" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.48</v>
+        <v>2.68</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.64</v>
+        <v>3.71</v>
       </c>
       <c r="R167" t="n">
-        <v>7.9</v>
+        <v>2.68</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF170" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>5.87</v>
+        <v>2.07</v>
       </c>
       <c r="Q171" t="n">
-        <v>5.56</v>
+        <v>3.93</v>
       </c>
       <c r="R171" t="n">
-        <v>1.5</v>
+        <v>3.62</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.82</v>
+        <v>3.39</v>
       </c>
       <c r="R172" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.15</v>
+        <v>1.37</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="R174" t="n">
-        <v>3.54</v>
+        <v>8.75</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="R175" t="n">
-        <v>3.62</v>
+        <v>4.42</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF175" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="R177" t="n">
-        <v>5.04</v>
+        <v>3.54</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.39</v>
+        <v>3.82</v>
       </c>
       <c r="R182" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.13</v>
+        <v>3.96</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>5.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>4.82</v>
+        <v>2.78</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="R38" t="n">
-        <v>5.41</v>
+        <v>4.18</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.99</v>
+        <v>2.71</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>3.68</v>
       </c>
       <c r="R39" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="R40" t="n">
-        <v>2.27</v>
+        <v>6.02</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.49</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>4.18</v>
+        <v>2.27</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.07</v>
+        <v>1.36</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="R44" t="n">
-        <v>2.15</v>
+        <v>8.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.36</v>
+        <v>3.07</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.9</v>
+        <v>3.99</v>
       </c>
       <c r="R48" t="n">
-        <v>8.25</v>
+        <v>2.15</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.71</v>
+        <v>5.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.68</v>
+        <v>4.59</v>
       </c>
       <c r="R49" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>3.03</v>
+        <v>2.48</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.93</v>
+        <v>3.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="R71" t="n">
-        <v>4.27</v>
+        <v>2</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.72</v>
+        <v>1.93</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>2</v>
+        <v>4.27</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>2.34</v>
+        <v>4.17</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.12</v>
+        <v>1.21</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>6.11</v>
       </c>
       <c r="R77" t="n">
-        <v>3.6</v>
+        <v>9.91</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R79" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>3.17</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="R83" t="n">
-        <v>4.17</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="R91" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.71</v>
+        <v>5.8</v>
       </c>
       <c r="R105" t="n">
-        <v>3.69</v>
+        <v>8.65</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.23</v>
+        <v>2.69</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="R106" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.68</v>
+        <v>3.7</v>
       </c>
       <c r="R107" t="n">
-        <v>1.48</v>
+        <v>3.33</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="R108" t="n">
-        <v>8.65</v>
+        <v>4.4</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q141" t="n">
-        <v>6.35</v>
+        <v>3.6</v>
       </c>
       <c r="R141" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="R145" t="n">
-        <v>2.87</v>
+        <v>6.05</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.24</v>
+        <v>4.25</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.52</v>
+        <v>4.25</v>
       </c>
       <c r="R148" t="n">
-        <v>3.32</v>
+        <v>1.78</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.33</v>
+        <v>1.31</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.24</v>
+        <v>6.35</v>
       </c>
       <c r="R150" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R153" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R154" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.78</v>
+        <v>5.87</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.39</v>
+        <v>5.56</v>
       </c>
       <c r="R172" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.75</v>
+        <v>3.82</v>
       </c>
       <c r="R174" t="n">
-        <v>8.75</v>
+        <v>2.58</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF175" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R177" t="n">
-        <v>3.54</v>
+        <v>4.42</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF177" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.81</v>
+        <v>2.78</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.71</v>
+        <v>3.39</v>
       </c>
       <c r="R181" t="n">
-        <v>5.15</v>
+        <v>2.78</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="R182" t="n">
-        <v>2.58</v>
+        <v>5.04</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF193" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.13</v>
+        <v>3.96</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>5.97</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="R29" t="n">
-        <v>5.97</v>
+        <v>6.43</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.72</v>
+        <v>3.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="R38" t="n">
-        <v>4.18</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>3.46</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="R40" t="n">
-        <v>6.02</v>
+        <v>5.41</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.99</v>
+        <v>5.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
       <c r="R43" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>3.46</v>
+        <v>2.27</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R46" t="n">
-        <v>5.82</v>
+        <v>6.02</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>4.49</v>
       </c>
       <c r="R47" t="n">
-        <v>2.7</v>
+        <v>4.18</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5.2</v>
+        <v>3.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.59</v>
+        <v>3.99</v>
       </c>
       <c r="R49" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>5.41</v>
+        <v>3.11</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="R62" t="n">
-        <v>4.46</v>
+        <v>5.41</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,16 +12666,16 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R63" t="n">
-        <v>2.47</v>
+        <v>3.96</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH63" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.62</v>
+        <v>1.27</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.82</v>
+        <v>5.9</v>
       </c>
       <c r="R64" t="n">
-        <v>2.33</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>5.41</v>
+        <v>4.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,16 +13257,16 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.27</v>
+        <v>2.62</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.9</v>
+        <v>3.82</v>
       </c>
       <c r="R66" t="n">
-        <v>9.050000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="R68" t="n">
-        <v>3.83</v>
+        <v>2.47</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,16 +13848,16 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R69" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.21</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.11</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>9.91</v>
+        <v>3.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>4.22</v>
+        <v>3.69</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.12</v>
+        <v>3.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="R79" t="n">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R87" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.23</v>
+        <v>1.99</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="R88" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="R89" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R91" t="n">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.11</v>
+        <v>8</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.71</v>
+        <v>4.68</v>
       </c>
       <c r="R97" t="n">
-        <v>3.69</v>
+        <v>1.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="R107" t="n">
-        <v>3.33</v>
+        <v>8.65</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.68</v>
+        <v>2.69</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="R108" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R121" t="n">
-        <v>5.54</v>
+        <v>2.27</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R122" t="n">
-        <v>2.27</v>
+        <v>5.54</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R125" t="n">
-        <v>4.44</v>
+        <v>2.22</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.08</v>
+        <v>3.01</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.71</v>
+        <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>3.21</v>
+        <v>2.47</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.01</v>
+        <v>2.08</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.1</v>
+        <v>3.71</v>
       </c>
       <c r="R139" t="n">
-        <v>2.47</v>
+        <v>3.21</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R144" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="Q145" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="R145" t="n">
-        <v>6.05</v>
+        <v>2.87</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R147" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>4.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="R148" t="n">
-        <v>1.78</v>
+        <v>3.32</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.31</v>
+        <v>2.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>6.35</v>
+        <v>3.4</v>
       </c>
       <c r="R150" t="n">
-        <v>9</v>
+        <v>2.84</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.6</v>
+        <v>6.35</v>
       </c>
       <c r="R152" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R153" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="R154" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.93</v>
+        <v>3.71</v>
       </c>
       <c r="R166" t="n">
-        <v>3.62</v>
+        <v>2.68</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD168" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.71</v>
+        <v>3.39</v>
       </c>
       <c r="R169" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.56</v>
+        <v>3.71</v>
       </c>
       <c r="R172" t="n">
-        <v>1.5</v>
+        <v>5.15</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.73</v>
+        <v>1.37</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.82</v>
+        <v>5.75</v>
       </c>
       <c r="R174" t="n">
-        <v>2.58</v>
+        <v>8.75</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.68</v>
+        <v>3.93</v>
       </c>
       <c r="R177" t="n">
-        <v>4.42</v>
+        <v>3.62</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF177" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R183" t="n">
-        <v>5.15</v>
+        <v>4.42</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.07</v>
+        <v>4.78</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>5.13</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>5.97</v>
+        <v>4.78</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.78</v>
+        <v>4.82</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>4.78</v>
+        <v>2.7</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.15</v>
+        <v>3.11</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.76</v>
+        <v>4.49</v>
       </c>
       <c r="R39" t="n">
-        <v>3.46</v>
+        <v>4.18</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>3.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.7</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>5.41</v>
+        <v>2.15</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R41" t="n">
-        <v>5.82</v>
+        <v>6.02</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.59</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
         <v>4.9</v>
       </c>
       <c r="R44" t="n">
-        <v>8.25</v>
+        <v>5.82</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9126,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>4.59</v>
       </c>
       <c r="R45" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R46" t="n">
-        <v>6.02</v>
+        <v>8.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.72</v>
+        <v>3.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="R47" t="n">
-        <v>4.18</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R48" t="n">
-        <v>2.7</v>
+        <v>5.41</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.99</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="R50" t="n">
-        <v>3.11</v>
+        <v>3.46</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.92</v>
+        <v>3.27</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10851,7 +10851,7 @@
         <v>2.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
         <v>2.48</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.17</v>
+        <v>3.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R57" t="n">
-        <v>3.03</v>
+        <v>1.96</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="R62" t="n">
-        <v>5.41</v>
+        <v>2.47</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,16 +12666,16 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="R63" t="n">
-        <v>3.96</v>
+        <v>2.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.9</v>
+        <v>4.55</v>
       </c>
       <c r="R64" t="n">
-        <v>9.050000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="R65" t="n">
-        <v>4.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,16 +13257,16 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="R66" t="n">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13660,7 +13660,7 @@
         <v>2</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R68" t="n">
-        <v>2.47</v>
+        <v>3.96</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,16 +13848,16 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH68" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>3.83</v>
+        <v>4.46</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>4.22</v>
       </c>
       <c r="R74" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.72</v>
+        <v>1.93</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>4.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.17</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>2.34</v>
+        <v>3.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.22</v>
+        <v>3.68</v>
       </c>
       <c r="R80" t="n">
-        <v>4.22</v>
+        <v>2.34</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R88" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.23</v>
+        <v>1.99</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="R89" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R90" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="R91" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="R103" t="n">
-        <v>3.69</v>
+        <v>2.85</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="Q107" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="R107" t="n">
-        <v>8.65</v>
+        <v>4.4</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21686,10 +21686,10 @@
         <v>2.69</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="R108" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R121" t="n">
-        <v>2.27</v>
+        <v>5.54</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R122" t="n">
-        <v>5.54</v>
+        <v>2.27</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25477,10 +25477,10 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="R134" t="n">
-        <v>2.47</v>
+        <v>3.84</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R142" t="n">
-        <v>3.49</v>
+        <v>3.8</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.37</v>
+        <v>1.31</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.6</v>
+        <v>6.35</v>
       </c>
       <c r="R145" t="n">
-        <v>2.87</v>
+        <v>9</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R147" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R149" t="n">
-        <v>6.05</v>
+        <v>2.84</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="R150" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.31</v>
+        <v>2.89</v>
       </c>
       <c r="Q152" t="n">
-        <v>6.35</v>
+        <v>3.7</v>
       </c>
       <c r="R152" t="n">
-        <v>9</v>
+        <v>2.19</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.24</v>
+        <v>4.7</v>
       </c>
       <c r="R153" t="n">
-        <v>3.4</v>
+        <v>6.05</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>4.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R154" t="n">
-        <v>1.78</v>
+        <v>2.87</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>5.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q167" t="n">
-        <v>5.56</v>
+        <v>3.71</v>
       </c>
       <c r="R167" t="n">
-        <v>1.5</v>
+        <v>5.15</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="R168" t="n">
-        <v>3.32</v>
+        <v>2.78</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD168" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.78</v>
+        <v>5.87</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.39</v>
+        <v>5.56</v>
       </c>
       <c r="R169" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="R170" t="n">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R171" t="n">
-        <v>5.04</v>
+        <v>8.75</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="R172" t="n">
-        <v>5.15</v>
+        <v>5.04</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.75</v>
+        <v>3.93</v>
       </c>
       <c r="R174" t="n">
-        <v>8.75</v>
+        <v>3.62</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35512,10 +35512,10 @@
         <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD178" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R183" t="n">
-        <v>4.42</v>
+        <v>3.54</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.37</v>
+        <v>3.63</v>
       </c>
       <c r="R197" t="n">
-        <v>3.21</v>
+        <v>4.74</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39464,10 +39464,10 @@
         <v>0</v>
       </c>
       <c r="AG198" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH198" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF208" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.7</v>
+        <v>4.78</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.78</v>
+        <v>4.82</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.49</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>4.18</v>
+        <v>2.27</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.07</v>
+        <v>1.36</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="R40" t="n">
-        <v>2.15</v>
+        <v>8.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.47</v>
+        <v>2.71</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.1</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
-        <v>6.02</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.71</v>
+        <v>5.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>4.59</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R44" t="n">
-        <v>5.82</v>
+        <v>6.02</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9126,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.59</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.58</v>
+        <v>3.46</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R46" t="n">
-        <v>8.25</v>
+        <v>5.41</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="R48" t="n">
-        <v>5.41</v>
+        <v>4.18</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>2.27</v>
+        <v>5.82</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>3.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>2.48</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R62" t="n">
-        <v>2.47</v>
+        <v>3.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,16 +12666,16 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH62" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="R63" t="n">
-        <v>2.33</v>
+        <v>3.83</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="R64" t="n">
-        <v>5.41</v>
+        <v>3.58</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="R66" t="n">
-        <v>3.58</v>
+        <v>5.41</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q67" t="n">
         <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>3.83</v>
+        <v>2</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>3.96</v>
+        <v>4.46</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,16 +13848,16 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>4.46</v>
+        <v>2.33</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,55 +15182,55 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="R75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF75" t="n">
         <v>2</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>2.1</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="R80" t="n">
-        <v>2.34</v>
+        <v>4.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.21</v>
+        <v>3.72</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.11</v>
+        <v>4.05</v>
       </c>
       <c r="R86" t="n">
-        <v>9.91</v>
+        <v>2</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>3.23</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="R87" t="n">
-        <v>3.01</v>
+        <v>2.23</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="R88" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="R91" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="R96" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.58</v>
+        <v>5.8</v>
       </c>
       <c r="R103" t="n">
-        <v>2.85</v>
+        <v>8.65</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R121" t="n">
-        <v>5.54</v>
+        <v>2.27</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R122" t="n">
-        <v>2.27</v>
+        <v>5.54</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25477,10 +25477,10 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q128" t="n">
         <v>3.8</v>
       </c>
       <c r="R128" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>7.85</v>
+        <v>1.71</v>
       </c>
       <c r="Q131" t="n">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="R131" t="n">
-        <v>1.31</v>
+        <v>4.44</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.98</v>
+        <v>3.01</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>3.01</v>
+        <v>2.52</v>
       </c>
       <c r="Q137" t="n">
         <v>3.1</v>
       </c>
       <c r="R137" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH138" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>3.8</v>
+        <v>3.49</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="R143" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q144" t="n">
         <v>3.6</v>
       </c>
       <c r="R144" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R147" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="R148" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R149" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>4.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.25</v>
+        <v>6.35</v>
       </c>
       <c r="R150" t="n">
-        <v>1.78</v>
+        <v>9</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="R152" t="n">
-        <v>2.19</v>
+        <v>3.32</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="R153" t="n">
-        <v>6.05</v>
+        <v>2.87</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.37</v>
+        <v>4.25</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R154" t="n">
-        <v>2.87</v>
+        <v>1.78</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.03</v>
+        <v>4.29</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.81</v>
+        <v>2.68</v>
       </c>
       <c r="Q167" t="n">
         <v>3.71</v>
       </c>
       <c r="R167" t="n">
-        <v>5.15</v>
+        <v>2.68</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.78</v>
+        <v>5.87</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.39</v>
+        <v>5.56</v>
       </c>
       <c r="R168" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.71</v>
+        <v>3.39</v>
       </c>
       <c r="R170" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="Q171" t="n">
-        <v>5.75</v>
+        <v>3.93</v>
       </c>
       <c r="R171" t="n">
-        <v>8.75</v>
+        <v>3.62</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R172" t="n">
-        <v>5.04</v>
+        <v>8.75</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.93</v>
+        <v>3.71</v>
       </c>
       <c r="R174" t="n">
-        <v>3.62</v>
+        <v>5.15</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34921,10 +34921,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Q178" t="n">
-        <v>2.89</v>
+        <v>3.81</v>
       </c>
       <c r="R178" t="n">
-        <v>3.32</v>
+        <v>5.04</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35512,10 +35512,10 @@
         <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD178" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1.48</v>
+        <v>2.73</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.64</v>
+        <v>3.82</v>
       </c>
       <c r="R180" t="n">
-        <v>7.9</v>
+        <v>2.58</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R183" t="n">
-        <v>3.54</v>
+        <v>4.42</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,55 +39216,55 @@
         </is>
       </c>
       <c r="P197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF197" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="R197" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="S197" t="n">
-        <v>0</v>
-      </c>
-      <c r="T197" t="n">
-        <v>0</v>
-      </c>
-      <c r="U197" t="n">
-        <v>0</v>
-      </c>
-      <c r="V197" t="n">
-        <v>0</v>
-      </c>
-      <c r="W197" t="n">
-        <v>0</v>
-      </c>
-      <c r="X197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39464,10 +39464,10 @@
         <v>0</v>
       </c>
       <c r="AG198" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH198" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39661,10 +39661,10 @@
         <v>0</v>
       </c>
       <c r="AG199" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH199" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF208" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF209" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>3.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.96</v>
+        <v>2.13</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.29</v>
+        <v>5.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.08</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="R32" t="n">
-        <v>4.82</v>
+        <v>6.43</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>5.97</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>5.97</v>
+        <v>4.82</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R38" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.7</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="R39" t="n">
-        <v>2.27</v>
+        <v>5.41</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R40" t="n">
-        <v>8.25</v>
+        <v>6.02</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.71</v>
+        <v>3.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>5.2</v>
+        <v>3.99</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.59</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>4.49</v>
       </c>
       <c r="R43" t="n">
-        <v>3.11</v>
+        <v>4.18</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R44" t="n">
-        <v>6.02</v>
+        <v>5.82</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9126,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>3.46</v>
+        <v>2.27</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>5.41</v>
+        <v>2.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.49</v>
+        <v>3.76</v>
       </c>
       <c r="R48" t="n">
-        <v>4.18</v>
+        <v>3.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q49" t="n">
         <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>5.82</v>
+        <v>8.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.07</v>
+        <v>5.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
       <c r="R50" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="R60" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.6</v>
+        <v>3.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R61" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R63" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12872,7 +12872,7 @@
         <v>2</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.05</v>
+        <v>5.9</v>
       </c>
       <c r="R64" t="n">
-        <v>3.58</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="R65" t="n">
-        <v>9.050000000000001</v>
+        <v>3.83</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.51</v>
+        <v>3.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="R66" t="n">
-        <v>5.41</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>4.46</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,16 +13651,16 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.69</v>
+        <v>2.56</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="R68" t="n">
-        <v>4.46</v>
+        <v>2.47</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.62</v>
+        <v>4.55</v>
       </c>
       <c r="R70" t="n">
-        <v>2.47</v>
+        <v>5.41</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.17</v>
+        <v>1.21</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.68</v>
+        <v>6.11</v>
       </c>
       <c r="R75" t="n">
-        <v>2.34</v>
+        <v>9.91</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R80" t="n">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.02</v>
+        <v>3.17</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R82" t="n">
-        <v>3.69</v>
+        <v>2.34</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="R87" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R89" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="R91" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R121" t="n">
-        <v>2.27</v>
+        <v>5.54</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R122" t="n">
-        <v>5.54</v>
+        <v>2.27</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.82</v>
+        <v>3.86</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="R124" t="n">
-        <v>3.98</v>
+        <v>1.72</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>7.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q130" t="n">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="R130" t="n">
-        <v>1.31</v>
+        <v>2.22</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.71</v>
+        <v>7.85</v>
       </c>
       <c r="Q131" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="R131" t="n">
-        <v>4.44</v>
+        <v>1.31</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.01</v>
+        <v>2.52</v>
       </c>
       <c r="Q134" t="n">
         <v>3.1</v>
       </c>
       <c r="R134" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.98</v>
+        <v>3.01</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.71</v>
+        <v>3.99</v>
       </c>
       <c r="R139" t="n">
-        <v>3.21</v>
+        <v>3.84</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH139" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="R142" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R143" t="n">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.8</v>
+        <v>2.89</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R144" t="n">
-        <v>4.4</v>
+        <v>2.19</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.7</v>
+        <v>6.35</v>
       </c>
       <c r="R146" t="n">
-        <v>6.05</v>
+        <v>9</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R147" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R148" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R149" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R151" t="n">
-        <v>2.84</v>
+        <v>6.05</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R153" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.65</v>
+        <v>4.05</v>
       </c>
       <c r="R162" t="n">
-        <v>4.29</v>
+        <v>2.03</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.68</v>
+        <v>1.84</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R167" t="n">
-        <v>2.68</v>
+        <v>4.42</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>5.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q168" t="n">
-        <v>5.56</v>
+        <v>3.4</v>
       </c>
       <c r="R168" t="n">
-        <v>1.5</v>
+        <v>3.54</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.07</v>
+        <v>2.73</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="R171" t="n">
-        <v>3.62</v>
+        <v>2.58</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.75</v>
+        <v>3.81</v>
       </c>
       <c r="R172" t="n">
-        <v>8.75</v>
+        <v>5.04</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.15</v>
+        <v>5.87</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.4</v>
+        <v>5.56</v>
       </c>
       <c r="R173" t="n">
-        <v>3.54</v>
+        <v>1.5</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.89</v>
+        <v>3.93</v>
       </c>
       <c r="R175" t="n">
-        <v>3.32</v>
+        <v>3.62</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34921,10 +34921,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.81</v>
+        <v>2.89</v>
       </c>
       <c r="R178" t="n">
-        <v>5.04</v>
+        <v>3.32</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35512,10 +35512,10 @@
         <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD178" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="R183" t="n">
-        <v>4.42</v>
+        <v>2.78</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38861,10 +38861,10 @@
         <v>0</v>
       </c>
       <c r="AC195" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD195" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF198" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF208" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF209" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>3.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.96</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.13</v>
+        <v>3.96</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.73</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>6.43</v>
+        <v>2.78</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.78</v>
+        <v>5.97</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="R33" t="n">
-        <v>4.82</v>
+        <v>6.43</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R34" t="n">
-        <v>5.97</v>
+        <v>4.78</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R38" t="n">
-        <v>6.02</v>
+        <v>8.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.49</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>4.18</v>
+        <v>2.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.99</v>
+        <v>5.1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.15</v>
+        <v>6.02</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="R43" t="n">
-        <v>5.41</v>
+        <v>4.18</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5.2</v>
+        <v>3.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.59</v>
+        <v>3.99</v>
       </c>
       <c r="R44" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9126,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="R45" t="n">
-        <v>3.11</v>
+        <v>5.82</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.99</v>
+        <v>5.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3</v>
+        <v>3.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="R47" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.9</v>
+        <v>3.76</v>
       </c>
       <c r="R48" t="n">
-        <v>5.82</v>
+        <v>3.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9914,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R49" t="n">
-        <v>8.25</v>
+        <v>5.41</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>2.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q53" t="n">
         <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q56" t="n">
         <v>3.35</v>
       </c>
       <c r="R56" t="n">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.9</v>
+        <v>4.55</v>
       </c>
       <c r="R62" t="n">
-        <v>9.050000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>3.96</v>
+        <v>4.46</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q64" t="n">
         <v>4.1</v>
       </c>
       <c r="R64" t="n">
-        <v>3.83</v>
+        <v>2</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.05</v>
+        <v>5.9</v>
       </c>
       <c r="R65" t="n">
-        <v>3.58</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R66" t="n">
-        <v>2.47</v>
+        <v>3.96</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,16 +13454,16 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH66" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>2.33</v>
+        <v>3.83</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="R69" t="n">
-        <v>5.41</v>
+        <v>2.47</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R70" t="n">
-        <v>4.46</v>
+        <v>3.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.02</v>
+        <v>3.72</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R78" t="n">
-        <v>3.69</v>
+        <v>2</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,133 +17152,133 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R85" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS85" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW85" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY85" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA85" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB85" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,133 +17349,133 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="S86" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK86" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS86" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV86" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX86" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY86" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ86" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BA86" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>4.22</v>
+        <v>3.69</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.23</v>
+        <v>1.97</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.24</v>
+        <v>3.85</v>
       </c>
       <c r="R89" t="n">
-        <v>2.23</v>
+        <v>3.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R90" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R91" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="R92" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.69</v>
+        <v>2.11</v>
       </c>
       <c r="Q103" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R103" t="n">
         <v>3.69</v>
-      </c>
-      <c r="R103" t="n">
-        <v>2.69</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.83</v>
+        <v>3.86</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R126" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25280,10 +25280,10 @@
         <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.71</v>
+        <v>7.85</v>
       </c>
       <c r="Q131" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="R131" t="n">
-        <v>4.44</v>
+        <v>1.31</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R132" t="n">
-        <v>3.98</v>
+        <v>2.19</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.08</v>
+        <v>3.01</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.71</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>3.21</v>
+        <v>2.47</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>2.19</v>
+        <v>3.49</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,79 +28578,79 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="Q143" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="R143" t="n">
-        <v>12</v>
+        <v>6.05</v>
       </c>
       <c r="S143" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL143" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
@@ -28659,52 +28659,52 @@
         <v>0</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="n">
         <v>0</v>
       </c>
       <c r="AV143" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW143" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AX143" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AY143" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC143" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE143" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,133 +28972,133 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q145" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R145" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="S145" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI145" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK145" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL145" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM145" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO145" t="n">
         <v>0</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS145" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV145" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX145" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY145" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ145" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA145" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB145" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC145" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD145" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE145" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF145" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q146" t="n">
-        <v>6.35</v>
+        <v>3.6</v>
       </c>
       <c r="R146" t="n">
-        <v>9</v>
+        <v>2.87</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R147" t="n">
-        <v>3.6</v>
+        <v>1.78</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.6</v>
+        <v>1.31</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.4</v>
+        <v>6.35</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>9</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,133 +29760,133 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="Q149" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T149" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U149" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X149" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA149" t="n">
         <v>3.6</v>
       </c>
-      <c r="R149" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>0</v>
-      </c>
       <c r="BB149" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC149" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD149" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE149" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF149" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,133 +29957,133 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>4.82</v>
+        <v>1.18</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.12</v>
+        <v>7</v>
       </c>
       <c r="R150" t="n">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="S150" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="T150" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="U150" t="n">
-        <v>2.15</v>
+        <v>9</v>
       </c>
       <c r="V150" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W150" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X150" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ150" t="n">
         <v>1.3</v>
       </c>
-      <c r="W150" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X150" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK150" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL150" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.18</v>
+        <v>4.3</v>
       </c>
       <c r="AO150" t="n">
         <v>0</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AS150" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU150" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV150" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="AX150" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="AY150" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AZ150" t="n">
-        <v>3.4</v>
+        <v>1.08</v>
       </c>
       <c r="BA150" t="n">
-        <v>1.41</v>
+        <v>9</v>
       </c>
       <c r="BB150" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="BC150" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="BD150" t="n">
-        <v>4.35</v>
+        <v>6.4</v>
       </c>
       <c r="BE150" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="BF150" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,133 +30154,133 @@
         </is>
       </c>
       <c r="P151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R151" t="n">
+        <v>5</v>
+      </c>
+      <c r="S151" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U151" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V151" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W151" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X151" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL151" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q151" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R151" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" t="n">
-        <v>0</v>
-      </c>
-      <c r="W151" t="n">
-        <v>0</v>
-      </c>
-      <c r="X151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL151" t="n">
-        <v>0</v>
-      </c>
       <c r="AM151" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO151" t="n">
         <v>0</v>
       </c>
       <c r="AP151" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR151" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS151" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU151" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV151" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW151" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX151" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY151" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ151" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB151" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC151" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD151" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE151" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF151" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R152" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,133 +30548,133 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="R153" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="S153" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V153" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X153" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD153" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI153" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ153" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO153" t="n">
         <v>0</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR153" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS153" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV153" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW153" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX153" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY153" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ153" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB153" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC153" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD153" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE153" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF153" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,133 +30942,133 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.53</v>
+        <v>4.82</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.7</v>
+        <v>4.12</v>
       </c>
       <c r="R155" t="n">
-        <v>6.05</v>
+        <v>1.66</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V155" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z155" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC155" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD155" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI155" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK155" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL155" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM155" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN155" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO155" t="n">
         <v>0</v>
       </c>
       <c r="AP155" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR155" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS155" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU155" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV155" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW155" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX155" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY155" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ155" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA155" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB155" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC155" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD155" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE155" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF155" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R157" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>4.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="R158" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="R167" t="n">
-        <v>2.03</v>
+        <v>4.29</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="R171" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.78</v>
+        <v>1.37</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.39</v>
+        <v>5.75</v>
       </c>
       <c r="R172" t="n">
-        <v>2.78</v>
+        <v>8.75</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="R178" t="n">
-        <v>2.68</v>
+        <v>5.04</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="R179" t="n">
-        <v>5.04</v>
+        <v>5.15</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="Q181" t="n">
-        <v>5.75</v>
+        <v>3.82</v>
       </c>
       <c r="R181" t="n">
-        <v>8.75</v>
+        <v>2.58</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="R183" t="n">
-        <v>4.42</v>
+        <v>3.32</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36497,16 +36497,16 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD183" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="R188" t="n">
-        <v>3.32</v>
+        <v>4.42</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37482,16 +37482,16 @@
         <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,55 +39216,55 @@
         </is>
       </c>
       <c r="P197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF197" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="R197" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="S197" t="n">
-        <v>0</v>
-      </c>
-      <c r="T197" t="n">
-        <v>0</v>
-      </c>
-      <c r="U197" t="n">
-        <v>0</v>
-      </c>
-      <c r="V197" t="n">
-        <v>0</v>
-      </c>
-      <c r="W197" t="n">
-        <v>0</v>
-      </c>
-      <c r="X197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39452,10 +39452,10 @@
         <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD198" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.02</v>
+        <v>3.63</v>
       </c>
       <c r="R200" t="n">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40049,10 +40049,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF201" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40240,10 +40240,10 @@
         <v>0</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD202" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE202" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G208" t="n">

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>5.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="R5" t="n">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.49</v>
+        <v>4.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>3.39</v>
       </c>
       <c r="R28" t="n">
-        <v>5.97</v>
+        <v>1.88</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.73</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>6.43</v>
+        <v>4.82</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.36</v>
+        <v>2.71</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.9</v>
+        <v>3.68</v>
       </c>
       <c r="R38" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="R40" t="n">
-        <v>2.7</v>
+        <v>8.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="R41" t="n">
         <v>2.15</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.11</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="R42" t="n">
-        <v>6.02</v>
+        <v>5.41</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.72</v>
+        <v>5.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.49</v>
+        <v>4.59</v>
       </c>
       <c r="R43" t="n">
-        <v>4.18</v>
+        <v>1.58</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.99</v>
+        <v>3.76</v>
       </c>
       <c r="R44" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>5.82</v>
+        <v>2.27</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.59</v>
+        <v>5.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.58</v>
+        <v>6.02</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.99</v>
+        <v>1.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
       <c r="R47" t="n">
-        <v>1.85</v>
+        <v>4.18</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>3.46</v>
+        <v>3.11</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>5.41</v>
+        <v>5.82</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.71</v>
+        <v>3.99</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="R50" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>3.31</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R55" t="n">
-        <v>3.27</v>
+        <v>1.96</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="R62" t="n">
-        <v>5.41</v>
+        <v>3.58</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="R63" t="n">
-        <v>4.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>5.41</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="R65" t="n">
-        <v>9.050000000000001</v>
+        <v>3.83</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R66" t="n">
-        <v>3.96</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R67" t="n">
-        <v>3.83</v>
+        <v>3.96</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="R68" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,16 +13848,16 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>3.58</v>
+        <v>4.46</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.96</v>
+        <v>10.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="R73" t="n">
-        <v>4.17</v>
+        <v>1.22</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.72</v>
+        <v>1.96</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>4.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.17</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>2.34</v>
+        <v>3.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.13</v>
+        <v>3.23</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="R88" t="n">
-        <v>3.01</v>
+        <v>2.23</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="R91" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.23</v>
+        <v>1.99</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="R92" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.69</v>
+        <v>2.11</v>
       </c>
       <c r="Q93" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R93" t="n">
         <v>3.69</v>
-      </c>
-      <c r="R93" t="n">
-        <v>2.69</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.68</v>
+        <v>2.69</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="R99" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R124" t="n">
-        <v>2.22</v>
+        <v>4.44</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25280,10 +25280,10 @@
         <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="Q127" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R127" t="n">
-        <v>4.44</v>
+        <v>2.22</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.82</v>
+        <v>3.86</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="R129" t="n">
-        <v>3.98</v>
+        <v>1.72</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.08</v>
+        <v>3.01</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.71</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>3.21</v>
+        <v>2.47</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="R137" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>3.01</v>
+        <v>2.52</v>
       </c>
       <c r="Q138" t="n">
         <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.99</v>
+        <v>3.71</v>
       </c>
       <c r="R139" t="n">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Q143" t="n">
-        <v>4.7</v>
+        <v>6.35</v>
       </c>
       <c r="R143" t="n">
-        <v>6.05</v>
+        <v>9</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.37</v>
+        <v>4.25</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R146" t="n">
-        <v>2.87</v>
+        <v>1.78</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,133 +29366,133 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R147" t="n">
-        <v>1.78</v>
+        <v>4.75</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V147" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD147" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF147" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG147" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH147" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI147" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK147" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL147" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM147" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO147" t="n">
         <v>0</v>
       </c>
       <c r="AP147" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR147" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS147" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU147" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV147" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX147" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY147" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ147" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA147" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB147" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC147" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD147" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE147" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF147" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,79 +29563,79 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Q148" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="R148" t="n">
+        <v>12</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T148" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U148" t="n">
         <v>9</v>
       </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
       <c r="V148" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W148" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X148" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC148" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD148" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF148" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG148" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH148" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI148" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL148" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM148" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN148" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AO148" t="n">
         <v>0</v>
@@ -29644,52 +29644,52 @@
         <v>0</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR148" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS148" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU148" t="n">
         <v>0</v>
       </c>
       <c r="AV148" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW148" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX148" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AY148" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ148" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA148" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB148" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC148" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD148" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE148" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BF148" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,133 +29760,133 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q149" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R149" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="S149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH149" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK149" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM149" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO149" t="n">
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX149" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY149" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ149" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA149" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB149" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC149" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD149" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE149" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,79 +29957,79 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.18</v>
+        <v>2.33</v>
       </c>
       <c r="Q150" t="n">
-        <v>7</v>
+        <v>3.24</v>
       </c>
       <c r="R150" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="S150" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X150" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD150" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL150" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN150" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AO150" t="n">
         <v>0</v>
@@ -30038,52 +30038,52 @@
         <v>0</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="n">
         <v>0</v>
       </c>
       <c r="AV150" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW150" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AX150" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AY150" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ150" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BA150" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB150" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC150" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD150" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE150" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF150" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG150" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,133 +30942,133 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>4.82</v>
+        <v>2.89</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.12</v>
+        <v>3.7</v>
       </c>
       <c r="R155" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="S155" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V155" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK155" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL155" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN155" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO155" t="n">
         <v>0</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS155" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV155" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW155" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AX155" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY155" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ155" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA155" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BB155" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC155" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD155" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE155" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF155" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R157" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,133 +31533,133 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.33</v>
+        <v>4.82</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.24</v>
+        <v>4.12</v>
       </c>
       <c r="R158" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S158" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W158" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="X158" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ158" t="n">
         <v>3.4</v>
       </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" t="n">
-        <v>0</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ158" t="n">
-        <v>0</v>
-      </c>
       <c r="BA158" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB158" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC158" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD158" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF158" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R159" t="n">
-        <v>2.19</v>
+        <v>4.4</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32754,10 +32754,10 @@
         <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD164" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE164" t="n">
         <v>0</v>
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="R166" t="n">
-        <v>2.03</v>
+        <v>4.29</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD168" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33739,10 +33739,10 @@
         <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD169" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33936,10 +33936,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD170" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="R171" t="n">
-        <v>3.62</v>
+        <v>5.04</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.75</v>
+        <v>4.64</v>
       </c>
       <c r="R172" t="n">
-        <v>8.75</v>
+        <v>7.9</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>5.87</v>
+        <v>2.44</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.56</v>
+        <v>2.69</v>
       </c>
       <c r="R174" t="n">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34724,10 +34724,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34921,10 +34921,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.78</v>
+        <v>5.87</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.39</v>
+        <v>5.56</v>
       </c>
       <c r="R176" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>1.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="R178" t="n">
-        <v>5.04</v>
+        <v>2.58</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R179" t="n">
-        <v>5.15</v>
+        <v>4.42</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="R181" t="n">
-        <v>2.58</v>
+        <v>5.15</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q183" t="n">
-        <v>2.89</v>
+        <v>5.75</v>
       </c>
       <c r="R183" t="n">
-        <v>3.32</v>
+        <v>8.75</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36497,10 +36497,10 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37285,10 +37285,10 @@
         <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD187" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R188" t="n">
-        <v>4.42</v>
+        <v>3.54</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38073,10 +38073,10 @@
         <v>0</v>
       </c>
       <c r="AC191" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD191" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE191" t="n">
         <v>0</v>
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38270,10 +38270,10 @@
         <v>0</v>
       </c>
       <c r="AC192" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD192" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE192" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.37</v>
+        <v>3.63</v>
       </c>
       <c r="R197" t="n">
-        <v>3.21</v>
+        <v>4.74</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="R198" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39452,16 +39452,16 @@
         <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF198" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q199" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="R199" t="n">
-        <v>4.26</v>
+        <v>3.42</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39649,10 +39649,10 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD199" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.63</v>
+        <v>3.02</v>
       </c>
       <c r="R200" t="n">
-        <v>4.74</v>
+        <v>4.26</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41822,10 +41822,10 @@
         <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF210" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF213" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R214" t="n">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42610,10 +42610,10 @@
         <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AF214" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG214" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43004,10 +43004,10 @@
         <v>0</v>
       </c>
       <c r="AE216" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF216" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43201,10 +43201,10 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF217" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>5.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="R2" t="n">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.13</v>
+        <v>3.96</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5.38</v>
+        <v>3.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.23</v>
+        <v>1.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.39</v>
+        <v>4.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.88</v>
+        <v>6.43</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>4.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="R29" t="n">
-        <v>4.78</v>
+        <v>1.88</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
-        <v>5.97</v>
+        <v>4.78</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.73</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>6.43</v>
+        <v>4.82</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.71</v>
+        <v>1.47</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.68</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>6.02</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.36</v>
+        <v>3.99</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.9</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>8.25</v>
+        <v>1.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="R42" t="n">
-        <v>5.41</v>
+        <v>5.82</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.59</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.76</v>
+        <v>4.49</v>
       </c>
       <c r="R44" t="n">
-        <v>3.46</v>
+        <v>4.18</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="R45" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R46" t="n">
-        <v>6.02</v>
+        <v>8.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9520,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.49</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>4.18</v>
+        <v>3.11</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="R48" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.9</v>
+        <v>3.76</v>
       </c>
       <c r="R49" t="n">
-        <v>5.82</v>
+        <v>3.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.99</v>
+        <v>5.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
       <c r="R50" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="R54" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>3.17</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R58" t="n">
-        <v>3.27</v>
+        <v>2.32</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12033,7 +12033,7 @@
         <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
         <v>2.48</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>2.48</v>
+        <v>3.03</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="R62" t="n">
-        <v>3.58</v>
+        <v>5.41</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.27</v>
+        <v>2.62</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.9</v>
+        <v>3.82</v>
       </c>
       <c r="R63" t="n">
-        <v>9.050000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="R64" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R65" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13266,7 +13266,7 @@
         <v>2</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,16 +13454,16 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>3.96</v>
+        <v>4.46</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,16 +13651,16 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="R68" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,16 +13848,16 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="R69" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="R70" t="n">
-        <v>4.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>10.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>1.22</v>
+        <v>4.17</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.96</v>
+        <v>3.72</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R78" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>3.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R79" t="n">
-        <v>3.69</v>
+        <v>2.34</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.72</v>
+        <v>2.02</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>3.69</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="R83" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF83" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,133 +17152,133 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R85" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="S85" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV85" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BA85" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.12</v>
+        <v>1.21</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>6.11</v>
       </c>
       <c r="R86" t="n">
-        <v>3.6</v>
+        <v>9.91</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R89" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="R91" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R92" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="R98" t="n">
-        <v>3.33</v>
+        <v>5.74</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>4.23</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="R104" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="R115" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="Q124" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R124" t="n">
-        <v>4.44</v>
+        <v>2.19</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R128" t="n">
-        <v>3.98</v>
+        <v>2.22</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="R129" t="n">
-        <v>1.72</v>
+        <v>3.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.83</v>
+        <v>3.86</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R132" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>3.01</v>
+        <v>7</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R136" t="n">
-        <v>2.47</v>
+        <v>1.3</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.99</v>
+        <v>3.71</v>
       </c>
       <c r="R137" t="n">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.52</v>
+        <v>3.01</v>
       </c>
       <c r="Q138" t="n">
         <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>2.91</v>
+        <v>2.47</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.71</v>
+        <v>3.99</v>
       </c>
       <c r="R139" t="n">
-        <v>3.21</v>
+        <v>3.84</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH139" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>7</v>
+        <v>2.52</v>
       </c>
       <c r="Q140" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>1.3</v>
+        <v>2.91</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q143" t="n">
-        <v>6.35</v>
+        <v>3.6</v>
       </c>
       <c r="R143" t="n">
-        <v>9</v>
+        <v>2.87</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="R144" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,133 +29169,133 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>4.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="R146" t="n">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V146" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W146" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X146" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD146" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG146" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH146" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI146" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK146" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL146" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM146" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN146" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO146" t="n">
         <v>0</v>
       </c>
       <c r="AP146" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR146" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS146" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU146" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV146" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW146" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX146" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY146" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ146" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB146" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC146" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD146" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE146" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF146" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,49 +29366,49 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.75</v>
+        <v>4.82</v>
       </c>
       <c r="Q147" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="R147" t="n">
-        <v>4.75</v>
+        <v>1.66</v>
       </c>
       <c r="S147" t="n">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="T147" t="n">
         <v>2.38</v>
       </c>
       <c r="U147" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="V147" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W147" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="X147" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z147" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AB147" t="n">
         <v>1.03</v>
       </c>
       <c r="AC147" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AD147" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AE147" t="n">
         <v>1.62</v>
@@ -29417,7 +29417,7 @@
         <v>2.15</v>
       </c>
       <c r="AG147" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH147" t="n">
         <v>1.44</v>
@@ -29429,67 +29429,67 @@
         <v>1.17</v>
       </c>
       <c r="AK147" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL147" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AM147" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN147" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AO147" t="n">
         <v>0</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AS147" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AU147" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AV147" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AW147" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AX147" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AY147" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ147" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="BA147" t="n">
-        <v>3.6</v>
+        <v>1.41</v>
       </c>
       <c r="BB147" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC147" t="n">
         <v>1.91</v>
       </c>
       <c r="BD147" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="BE147" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF147" t="n">
         <v>1.22</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,133 +29760,133 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q149" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T149" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U149" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X149" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU149" t="n">
         <v>3.5</v>
       </c>
-      <c r="R149" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>0</v>
-      </c>
       <c r="AV149" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX149" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY149" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ149" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA149" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB149" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC149" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD149" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE149" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF149" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R150" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,133 +30154,133 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.67</v>
+        <v>2.89</v>
       </c>
       <c r="Q151" t="n">
         <v>3.7</v>
       </c>
       <c r="R151" t="n">
-        <v>5</v>
+        <v>2.19</v>
       </c>
       <c r="S151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD151" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO151" t="n">
         <v>0</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR151" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS151" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV151" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX151" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY151" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ151" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB151" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC151" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD151" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE151" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF151" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="R152" t="n">
-        <v>2.87</v>
+        <v>6.05</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="R155" t="n">
-        <v>2.19</v>
+        <v>3.32</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R156" t="n">
-        <v>6.05</v>
+        <v>2.84</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="R157" t="n">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,133 +31533,133 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>4.82</v>
+        <v>1.31</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.12</v>
+        <v>6.35</v>
       </c>
       <c r="R158" t="n">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="S158" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL158" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AX158" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ158" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA158" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BB158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC158" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF158" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q159" t="n">
         <v>3.6</v>
       </c>
       <c r="R159" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32163,10 +32163,10 @@
         <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32754,10 +32754,10 @@
         <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE164" t="n">
         <v>0</v>
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="R169" t="n">
-        <v>5.76</v>
+        <v>4.36</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33739,10 +33739,10 @@
         <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AD169" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="R170" t="n">
-        <v>4.36</v>
+        <v>5.76</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33936,10 +33936,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AD170" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.48</v>
+        <v>5.87</v>
       </c>
       <c r="Q172" t="n">
-        <v>4.64</v>
+        <v>5.56</v>
       </c>
       <c r="R172" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="Q174" t="n">
-        <v>2.69</v>
+        <v>3.82</v>
       </c>
       <c r="R174" t="n">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34724,10 +34724,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.71</v>
+        <v>3.39</v>
       </c>
       <c r="R175" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34921,10 +34921,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>5.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q176" t="n">
-        <v>5.56</v>
+        <v>3.81</v>
       </c>
       <c r="R176" t="n">
-        <v>1.5</v>
+        <v>5.04</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35315,10 +35315,10 @@
         <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD177" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.39</v>
+        <v>2.69</v>
       </c>
       <c r="R180" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35906,10 +35906,10 @@
         <v>0</v>
       </c>
       <c r="AC180" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD180" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE180" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="R181" t="n">
-        <v>5.15</v>
+        <v>3.54</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="R182" t="n">
-        <v>2.68</v>
+        <v>3.62</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q183" t="n">
-        <v>5.75</v>
+        <v>2.89</v>
       </c>
       <c r="R183" t="n">
-        <v>8.75</v>
+        <v>3.32</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36497,10 +36497,10 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD183" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.89</v>
+        <v>5.75</v>
       </c>
       <c r="R187" t="n">
-        <v>3.32</v>
+        <v>8.75</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37285,10 +37285,10 @@
         <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD187" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.4</v>
+        <v>4.64</v>
       </c>
       <c r="R188" t="n">
-        <v>3.54</v>
+        <v>7.9</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="R198" t="n">
-        <v>3.21</v>
+        <v>3.42</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39452,16 +39452,16 @@
         <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD198" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE198" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF198" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q199" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="R199" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39649,16 +39649,16 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF199" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.56</v>
+        <v>3.5</v>
       </c>
       <c r="R203" t="n">
-        <v>8.5</v>
+        <v>3.84</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,16 +40443,16 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG203" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH203" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>5.56</v>
       </c>
       <c r="R204" t="n">
-        <v>3.84</v>
+        <v>8.5</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,16 +40640,16 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH204" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AG204" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH204" t="n">
-        <v>0</v>
       </c>
       <c r="AI204" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41822,10 +41822,10 @@
         <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF210" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5.38</v>
+        <v>3.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>5.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.13</v>
+        <v>3.96</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>4.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="R23" t="n">
-        <v>4.33</v>
+        <v>1.63</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.78</v>
+        <v>4.78</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.48</v>
+        <v>4.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.73</v>
+        <v>3.39</v>
       </c>
       <c r="R28" t="n">
-        <v>6.43</v>
+        <v>1.88</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.23</v>
+        <v>1.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.39</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.88</v>
+        <v>4.82</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>4.82</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.47</v>
+        <v>3.99</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>3.99</v>
       </c>
       <c r="R38" t="n">
-        <v>6.02</v>
+        <v>1.85</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.71</v>
+        <v>1.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>4.9</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>5.82</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.59</v>
       </c>
       <c r="R41" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q42" t="n">
         <v>4.9</v>
       </c>
       <c r="R42" t="n">
-        <v>5.82</v>
+        <v>8.25</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R43" t="n">
-        <v>2.7</v>
+        <v>5.41</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.49</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>4.18</v>
+        <v>2.7</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.36</v>
+        <v>2.71</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.9</v>
+        <v>3.68</v>
       </c>
       <c r="R46" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>4.49</v>
       </c>
       <c r="R47" t="n">
-        <v>3.11</v>
+        <v>4.18</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.7</v>
+        <v>3.76</v>
       </c>
       <c r="R48" t="n">
-        <v>5.41</v>
+        <v>3.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>3.46</v>
+        <v>2.27</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>5.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.59</v>
+        <v>5.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.58</v>
+        <v>6.02</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.31</v>
+        <v>2.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
-        <v>1.96</v>
+        <v>2.92</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R53" t="n">
         <v>2.32</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R53" t="n">
-        <v>2.92</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.6</v>
+        <v>3.31</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R54" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.17</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>2.32</v>
+        <v>3.27</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>2.48</v>
+        <v>3.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R60" t="n">
-        <v>3.03</v>
+        <v>2.48</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
-        <v>5.41</v>
+        <v>4.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,16 +12666,16 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="R63" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="R64" t="n">
-        <v>3.83</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.62</v>
+        <v>4.55</v>
       </c>
       <c r="R66" t="n">
-        <v>2.47</v>
+        <v>5.41</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,16 +13454,16 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>2.56</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="R67" t="n">
-        <v>4.46</v>
+        <v>2.47</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R69" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="R70" t="n">
-        <v>9.050000000000001</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.72</v>
+        <v>2.02</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>3.69</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.68</v>
+        <v>3.26</v>
       </c>
       <c r="R79" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.02</v>
+        <v>3.72</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R82" t="n">
-        <v>3.69</v>
+        <v>2</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>3.17</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R83" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF83" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX83" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY83" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BA83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB83" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.26</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>2.27</v>
+        <v>4.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.12</v>
+        <v>10.2</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="R85" t="n">
-        <v>3.6</v>
+        <v>1.22</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,133 +17349,133 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.11</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>9.91</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK86" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM86" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS86" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA86" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB86" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R89" t="n">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R90" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R92" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R109" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="R115" t="n">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Q128" t="n">
         <v>3.8</v>
       </c>
       <c r="R128" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="Q130" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R130" t="n">
-        <v>4.44</v>
+        <v>2.22</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="R132" t="n">
-        <v>1.72</v>
+        <v>3.98</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>7</v>
+        <v>1.98</v>
       </c>
       <c r="Q136" t="n">
-        <v>5</v>
+        <v>3.99</v>
       </c>
       <c r="R136" t="n">
-        <v>1.3</v>
+        <v>3.84</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.71</v>
+        <v>5</v>
       </c>
       <c r="R137" t="n">
-        <v>3.21</v>
+        <v>1.3</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.98</v>
+        <v>3.01</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R139" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.1</v>
+        <v>3.71</v>
       </c>
       <c r="R140" t="n">
-        <v>2.91</v>
+        <v>3.21</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,79 +28381,79 @@
         </is>
       </c>
       <c r="P142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>7</v>
+      </c>
+      <c r="R142" t="n">
+        <v>12</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U142" t="n">
+        <v>9</v>
+      </c>
+      <c r="V142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W142" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL142" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q142" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="R142" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL142" t="n">
-        <v>0</v>
-      </c>
       <c r="AM142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
@@ -28462,52 +28462,52 @@
         <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR142" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS142" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU142" t="n">
         <v>0</v>
       </c>
       <c r="AV142" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW142" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX142" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AY142" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA142" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC142" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD142" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE142" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BF142" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>4.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q144" t="n">
-        <v>4.25</v>
+        <v>3.44</v>
       </c>
       <c r="R144" t="n">
-        <v>1.78</v>
+        <v>3.49</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,133 +28972,133 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V145" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W145" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD145" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG145" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH145" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI145" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ145" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK145" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL145" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM145" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN145" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO145" t="n">
         <v>0</v>
       </c>
       <c r="AP145" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR145" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS145" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU145" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV145" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW145" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX145" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY145" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ145" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA145" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB145" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC145" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD145" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE145" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF145" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,133 +29169,133 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.67</v>
+        <v>4.25</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="R146" t="n">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="S146" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X146" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG146" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH146" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI146" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ146" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK146" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL146" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM146" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN146" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO146" t="n">
         <v>0</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR146" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS146" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV146" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW146" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX146" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY146" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ146" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB146" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC146" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD146" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE146" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,133 +29366,133 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>4.82</v>
+        <v>1.67</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.12</v>
+        <v>3.7</v>
       </c>
       <c r="R147" t="n">
-        <v>1.66</v>
+        <v>5</v>
       </c>
       <c r="S147" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="T147" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U147" t="n">
-        <v>2.15</v>
+        <v>5.8</v>
       </c>
       <c r="V147" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W147" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X147" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH147" t="n">
         <v>1.3</v>
       </c>
-      <c r="W147" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X147" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI147" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK147" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AL147" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AM147" t="n">
         <v>1.22</v>
       </c>
       <c r="AN147" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="AO147" t="n">
         <v>0</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AS147" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="AT147" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AU147" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AV147" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AW147" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AX147" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AY147" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AZ147" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="BA147" t="n">
-        <v>1.41</v>
+        <v>3</v>
       </c>
       <c r="BB147" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC147" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="BD147" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="BE147" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="BF147" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,79 +29563,79 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Q148" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="R148" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S148" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG148" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI148" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL148" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN148" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AO148" t="n">
         <v>0</v>
@@ -29644,52 +29644,52 @@
         <v>0</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU148" t="n">
         <v>0</v>
       </c>
       <c r="AV148" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW148" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AX148" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AY148" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ148" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BA148" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB148" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC148" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD148" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE148" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF148" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,133 +29760,133 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="Q149" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R149" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="S149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH149" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK149" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL149" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM149" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO149" t="n">
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX149" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY149" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ149" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA149" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB149" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC149" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD149" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE149" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,133 +29957,133 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q150" t="n">
+        <v>4</v>
+      </c>
+      <c r="R150" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T150" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U150" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W150" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X150" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA150" t="n">
         <v>3.6</v>
       </c>
-      <c r="R150" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>0</v>
-      </c>
       <c r="BB150" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC150" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD150" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE150" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF150" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.89</v>
+        <v>1.97</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R151" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R154" t="n">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R155" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q156" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R156" t="n">
         <v>3.4</v>
-      </c>
-      <c r="R156" t="n">
-        <v>2.84</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.31</v>
+        <v>2.6</v>
       </c>
       <c r="Q158" t="n">
-        <v>6.35</v>
+        <v>3.4</v>
       </c>
       <c r="R158" t="n">
-        <v>9</v>
+        <v>2.84</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="R159" t="n">
-        <v>3.6</v>
+        <v>6.05</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32163,10 +32163,10 @@
         <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32360,10 +32360,10 @@
         <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>3.36</v>
+        <v>1.64</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="R168" t="n">
-        <v>2.29</v>
+        <v>5.76</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD168" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.64</v>
+        <v>3.36</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="R170" t="n">
-        <v>5.76</v>
+        <v>2.29</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33936,10 +33936,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD170" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.87</v>
+        <v>2.11</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.56</v>
+        <v>2.71</v>
       </c>
       <c r="R172" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34330,10 +34330,10 @@
         <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="R174" t="n">
-        <v>2.58</v>
+        <v>5.04</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.81</v>
+        <v>3.68</v>
       </c>
       <c r="R176" t="n">
-        <v>5.04</v>
+        <v>4.42</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="Q177" t="n">
-        <v>2.71</v>
+        <v>3.39</v>
       </c>
       <c r="R177" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35315,10 +35315,10 @@
         <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD177" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="R179" t="n">
-        <v>4.42</v>
+        <v>5.15</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF179" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.4</v>
+        <v>4.64</v>
       </c>
       <c r="R181" t="n">
-        <v>3.54</v>
+        <v>7.9</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36497,10 +36497,10 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.68</v>
+        <v>5.87</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.71</v>
+        <v>5.56</v>
       </c>
       <c r="R185" t="n">
-        <v>2.68</v>
+        <v>1.5</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37088,10 +37088,10 @@
         <v>0</v>
       </c>
       <c r="AC186" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD186" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="Q187" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="R187" t="n">
-        <v>8.75</v>
+        <v>3.54</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.48</v>
+        <v>2.68</v>
       </c>
       <c r="Q188" t="n">
-        <v>4.64</v>
+        <v>3.71</v>
       </c>
       <c r="R188" t="n">
-        <v>7.9</v>
+        <v>2.68</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
       <c r="Q191" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="R191" t="n">
-        <v>2.69</v>
+        <v>3.77</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38073,10 +38073,10 @@
         <v>0</v>
       </c>
       <c r="AC191" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD191" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE191" t="n">
         <v>0</v>
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="Q192" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="R192" t="n">
-        <v>3.77</v>
+        <v>2.69</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38270,10 +38270,10 @@
         <v>0</v>
       </c>
       <c r="AC192" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AD192" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AE192" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39452,10 +39452,10 @@
         <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE198" t="n">
         <v>0</v>
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q199" t="n">
-        <v>3.37</v>
+        <v>3.63</v>
       </c>
       <c r="R199" t="n">
-        <v>3.21</v>
+        <v>4.74</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF199" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.02</v>
+        <v>3.37</v>
       </c>
       <c r="R200" t="n">
-        <v>4.26</v>
+        <v>3.21</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39852,10 +39852,10 @@
         <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF200" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40043,10 +40043,10 @@
         <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD201" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF213" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42610,10 +42610,10 @@
         <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF214" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG214" t="n">
         <v>0</v>

--- a/jogos_2026-05-17.xlsx
+++ b/jogos_2026-05-17.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5.38</v>
+        <v>3.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.07</v>
+        <v>4.78</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>5.13</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>4.07</v>
       </c>
       <c r="R21" t="n">
-        <v>5.13</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>4.73</v>
       </c>
       <c r="R27" t="n">
-        <v>2.78</v>
+        <v>6.43</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.23</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.39</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.88</v>
+        <v>4.82</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.66</v>
+        <v>4.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="R29" t="n">
-        <v>4.82</v>
+        <v>1.88</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.99</v>
+        <v>1.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.85</v>
+        <v>8.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.9</v>
+        <v>4.59</v>
       </c>
       <c r="R39" t="n">
-        <v>5.82</v>
+        <v>1.58</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="R40" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.59</v>
+        <v>5.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.58</v>
+        <v>6.02</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.36</v>
+        <v>3.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.9</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>8.25</v>
+        <v>2.15</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.55</v>
+        <v>2.71</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="R43" t="n">
-        <v>5.41</v>
+        <v>2.5</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.07</v>
+        <v>3.99</v>
       </c>
       <c r="Q45" t="n">
         <v>3.99</v>
       </c>
       <c r="R45" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.68</v>
+        <v>4.49</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>4.18</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.49</v>
+        <v>4.9</v>
       </c>
       <c r="R47" t="n">
-        <v>4.18</v>
+        <v>5.82</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9717,10 +9717,10 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>3.46</v>
+        <v>2.27</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="R49" t="n">
-        <v>2.27</v>
+        <v>3.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>6.02</v>
+        <v>2.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.17</v>
+        <v>2.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.32</v>
+        <v>3.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.31</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>2.48</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R60" t="n">
-        <v>2.48</v>
+        <v>3.27</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R62" t="n">
-        <v>4.46</v>
+        <v>3.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,16 +12666,16 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="R63" t="n">
-        <v>3.96</v>
+        <v>2.47</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>9.050000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,16 +13060,16 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="R65" t="n">
-        <v>3.58</v>
+        <v>2.33</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.56</v>
+        <v>1.85</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R67" t="n">
-        <v>2.47</v>
+        <v>3.58</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,16 +13651,16 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="R68" t="n">
-        <v>2.33</v>
+        <v>3.83</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="R69" t="n">
-        <v>3.83</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.8</v>
+        <v>3.26</v>
       </c>
       <c r="R76" t="n">
-        <v>4.27</v>
+        <v>2.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,133 +15773,133 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q78" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U78" t="n">
         <v>3.4</v>
       </c>
-      <c r="R78" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="R79" t="n">
-        <v>2.27</v>
+        <v>4.27</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="Q81" t="n">
-        <v>6.11</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>9.91</v>
+        <v>3.69</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,55 +16561,55 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="R82" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF82" t="n">
         <v>2</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>2.1</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.17</v>
+        <v>2.12</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>2.34</v>
+        <v>3.6</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.22</v>
+        <v>6.11</v>
       </c>
       <c r="R84" t="n">
-        <v>4.22</v>
+        <v>9.91</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,133 +17349,133 @@
         </is>
       </c>
       <c r="P86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R86" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF86" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q86" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R86" t="n">
-        <v>3</v>
-      </c>
-      <c r="S86" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T86" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U86" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V86" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W86" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X86" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE86" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF86" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG86" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK86" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS86" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV86" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX86" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY86" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ86" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BA86" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="R88" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="R90" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R91" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.97</v>
+        <v>3.23</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.85</v>
+        <v>3.24</v>
       </c>
       <c r="R92" t="n">
-        <v>3.26</v>
+        <v>2.23</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R114" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="R115" t="n">
-        <v>3.69</v>
+        <v>2.7</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>4.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="R116" t="n">
-        <v>1.97</v>
+        <v>3.33</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q117" t="n">
-        <v>5.8</v>
+        <v>3.71</v>
       </c>
       <c r="R117" t="n">
-        <v>8.65</v>
+        <v>1.97</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="R119" t="n">
-        <v>3.33</v>
+        <v>2.85</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.69</v>
+        <v>8</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.69</v>
+        <v>4.68</v>
       </c>
       <c r="R120" t="n">
-        <v>2.69</v>
+        <v>1.48</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24247,10 +24247,10 @@
         <v>2.69</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="R121" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R122" t="n">
-        <v>5.54</v>
+        <v>2.27</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R123" t="n">
-        <v>2.27</v>
+        <v>5.54</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.71</v>
+        <v>3.86</v>
       </c>
       <c r="Q127" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R127" t="n">
-        <v>4.44</v>
+        <v>1.72</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25477,10 +25477,10 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.83</v>
+        <v>7.85</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.8</v>
+        <v>5.45</v>
       </c>
       <c r="R128" t="n">
-        <v>2.19</v>
+        <v>1.31</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>7.85</v>
+        <v>1.71</v>
       </c>
       <c r="Q131" t="n">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="R131" t="n">
-        <v>1.31</v>
+        <v>4.44</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.52</v>
+        <v>7</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R135" t="n">
-        <v>2.91</v>
+        <v>1.3</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
 